--- a/artfynd/A 37171-2024 artfynd.xlsx
+++ b/artfynd/A 37171-2024 artfynd.xlsx
@@ -1901,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119820205</v>
+        <v>119816953</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,43 +1913,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552627</v>
+        <v>552478</v>
       </c>
       <c r="R13" t="n">
-        <v>7063998</v>
+        <v>7064143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1991,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119816953</v>
+        <v>119820205</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2030,42 +2029,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552478</v>
+        <v>552627</v>
       </c>
       <c r="R14" t="n">
-        <v>7064143</v>
+        <v>7063998</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 37171-2024 artfynd.xlsx
+++ b/artfynd/A 37171-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819370</v>
+        <v>119817130</v>
       </c>
       <c r="B2" t="n">
         <v>57310</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552629</v>
+        <v>552524</v>
       </c>
       <c r="R2" t="n">
-        <v>7064013</v>
+        <v>7064101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819214</v>
+        <v>119820205</v>
       </c>
       <c r="B3" t="n">
-        <v>78262</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +808,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552621</v>
+        <v>552627</v>
       </c>
       <c r="R3" t="n">
-        <v>7063985</v>
+        <v>7063998</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,9 +870,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119818013</v>
+        <v>119819431</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,37 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552609</v>
+        <v>552620</v>
       </c>
       <c r="R4" t="n">
-        <v>7064097</v>
+        <v>7064000</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,9 +982,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119816855</v>
+        <v>119816881</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>4772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,46 +1033,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552478</v>
+        <v>552470</v>
       </c>
       <c r="R5" t="n">
-        <v>7064146</v>
+        <v>7064151</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,19 +1094,14 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:41</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119816881</v>
+        <v>119819214</v>
       </c>
       <c r="B6" t="n">
-        <v>4772</v>
+        <v>78262</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552470</v>
+        <v>552621</v>
       </c>
       <c r="R6" t="n">
-        <v>7064151</v>
+        <v>7063985</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,11 +1204,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119817063</v>
+        <v>119820977</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1253,10 +1263,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1265,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552512</v>
+        <v>552458</v>
       </c>
       <c r="R7" t="n">
-        <v>7064119</v>
+        <v>7064130</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,19 +1312,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1329,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119817132</v>
+        <v>119817767</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,27 +1357,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1382,13 +1386,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552557</v>
+        <v>552552</v>
       </c>
       <c r="R8" t="n">
-        <v>7064110</v>
+        <v>7064113</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,9 +1419,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,22 +1446,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119817200</v>
+        <v>119816973</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,34 +1474,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552555</v>
+        <v>552473</v>
       </c>
       <c r="R9" t="n">
-        <v>7064110</v>
+        <v>7064101</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,19 +1531,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,22 +1548,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819352</v>
+        <v>119818013</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,46 +1576,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552618</v>
+        <v>552609</v>
       </c>
       <c r="R10" t="n">
-        <v>7063975</v>
+        <v>7064097</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,7 +1662,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119817015</v>
+        <v>119819370</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1708,14 +1703,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552494</v>
+        <v>552629</v>
       </c>
       <c r="R11" t="n">
-        <v>7064121</v>
+        <v>7064013</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,7 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,7 +1779,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119817130</v>
+        <v>119818914</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1829,10 +1824,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552524</v>
+        <v>552569</v>
       </c>
       <c r="R12" t="n">
-        <v>7064101</v>
+        <v>7064094</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119816953</v>
+        <v>119819099</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,42 +1908,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552478</v>
+        <v>552600</v>
       </c>
       <c r="R13" t="n">
-        <v>7064143</v>
+        <v>7064081</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1976,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,7 +1986,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119820205</v>
+        <v>119817063</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -2058,14 +2054,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552627</v>
+        <v>552512</v>
       </c>
       <c r="R14" t="n">
-        <v>7063998</v>
+        <v>7064119</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2103,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819431</v>
+        <v>119819352</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2150,37 +2146,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552620</v>
+        <v>552618</v>
       </c>
       <c r="R15" t="n">
-        <v>7064000</v>
+        <v>7063975</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2207,19 +2212,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2234,22 +2229,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119820977</v>
+        <v>119816953</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2258,35 +2253,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2295,13 +2285,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552458</v>
+        <v>552478</v>
       </c>
       <c r="R16" t="n">
-        <v>7064130</v>
+        <v>7064143</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2328,9 +2318,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,22 +2345,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119817767</v>
+        <v>119817132</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2373,27 +2373,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552552</v>
+        <v>552557</v>
       </c>
       <c r="R17" t="n">
-        <v>7064113</v>
+        <v>7064110</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2435,19 +2435,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2462,22 +2452,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119818914</v>
+        <v>119817200</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,39 +2480,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552569</v>
+        <v>552555</v>
       </c>
       <c r="R18" t="n">
-        <v>7064094</v>
+        <v>7064110</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,7 +2539,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2564,7 +2549,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819099</v>
+        <v>119817015</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2632,14 +2617,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552600</v>
+        <v>552494</v>
       </c>
       <c r="R19" t="n">
-        <v>7064081</v>
+        <v>7064121</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,7 +2656,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2666,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119816973</v>
+        <v>119816855</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,34 +2709,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552473</v>
+        <v>552478</v>
       </c>
       <c r="R20" t="n">
-        <v>7064101</v>
+        <v>7064146</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,9 +2771,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,12 +2798,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 37171-2024 artfynd.xlsx
+++ b/artfynd/A 37171-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119817130</v>
+        <v>119819214</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>78262</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552524</v>
+        <v>552621</v>
       </c>
       <c r="R2" t="n">
-        <v>7064101</v>
+        <v>7063985</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,19 +748,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820205</v>
+        <v>119820977</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -825,25 +810,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552627</v>
+        <v>552458</v>
       </c>
       <c r="R3" t="n">
-        <v>7063998</v>
+        <v>7064130</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,19 +859,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819431</v>
+        <v>119818914</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +904,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552620</v>
+        <v>552569</v>
       </c>
       <c r="R4" t="n">
-        <v>7064000</v>
+        <v>7064094</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119816881</v>
+        <v>119819370</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,41 +1017,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552470</v>
+        <v>552629</v>
       </c>
       <c r="R5" t="n">
-        <v>7064151</v>
+        <v>7064013</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,14 +1083,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1110,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819214</v>
+        <v>119817200</v>
       </c>
       <c r="B6" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,37 +1138,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552621</v>
+        <v>552555</v>
       </c>
       <c r="R6" t="n">
-        <v>7063985</v>
+        <v>7064110</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,9 +1195,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,22 +1222,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820977</v>
+        <v>119818013</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,46 +1250,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552458</v>
+        <v>552609</v>
       </c>
       <c r="R7" t="n">
-        <v>7064130</v>
+        <v>7064097</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1336,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119817767</v>
+        <v>119819099</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1382,14 +1377,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552552</v>
+        <v>552600</v>
       </c>
       <c r="R8" t="n">
-        <v>7064113</v>
+        <v>7064081</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119816973</v>
+        <v>119816953</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,38 +1465,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552473</v>
+        <v>552478</v>
       </c>
       <c r="R9" t="n">
-        <v>7064101</v>
+        <v>7064143</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,9 +1530,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,22 +1557,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119818013</v>
+        <v>119819352</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,37 +1585,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552609</v>
+        <v>552618</v>
       </c>
       <c r="R10" t="n">
-        <v>7064097</v>
+        <v>7063975</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1662,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819370</v>
+        <v>119817015</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1703,14 +1721,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552629</v>
+        <v>552494</v>
       </c>
       <c r="R11" t="n">
-        <v>7064013</v>
+        <v>7064121</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1760,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1770,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,7 +1797,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119818914</v>
+        <v>119816855</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1820,14 +1838,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552569</v>
+        <v>552478</v>
       </c>
       <c r="R12" t="n">
-        <v>7064094</v>
+        <v>7064146</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819099</v>
+        <v>119816973</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,39 +1930,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552600</v>
+        <v>552473</v>
       </c>
       <c r="R13" t="n">
-        <v>7064081</v>
+        <v>7064101</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,19 +1987,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,12 +2004,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2130,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819352</v>
+        <v>119816881</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>4772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,50 +2145,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552618</v>
+        <v>552470</v>
       </c>
       <c r="R15" t="n">
-        <v>7063975</v>
+        <v>7064151</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2215,6 +2209,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,10 +2240,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119816953</v>
+        <v>119819431</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,42 +2252,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552478</v>
+        <v>552620</v>
       </c>
       <c r="R16" t="n">
-        <v>7064143</v>
+        <v>7064000</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2320,7 +2315,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2330,7 +2325,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2357,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119817132</v>
+        <v>119817767</v>
       </c>
       <c r="B17" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2373,27 +2368,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2402,13 +2397,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552557</v>
+        <v>552552</v>
       </c>
       <c r="R17" t="n">
-        <v>7064110</v>
+        <v>7064113</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2435,9 +2430,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,22 +2457,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119817200</v>
+        <v>119817130</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2480,34 +2485,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552555</v>
+        <v>552524</v>
       </c>
       <c r="R18" t="n">
-        <v>7064110</v>
+        <v>7064101</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2549,7 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,7 +2586,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119817015</v>
+        <v>119820205</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2617,14 +2627,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552494</v>
+        <v>552627</v>
       </c>
       <c r="R19" t="n">
-        <v>7064121</v>
+        <v>7063998</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2666,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2666,7 +2676,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2693,10 +2703,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119816855</v>
+        <v>119817132</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,27 +2719,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2738,13 +2748,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552478</v>
+        <v>552557</v>
       </c>
       <c r="R20" t="n">
-        <v>7064146</v>
+        <v>7064110</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2771,19 +2781,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,12 +2798,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 37171-2024 artfynd.xlsx
+++ b/artfynd/A 37171-2024 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119818914</v>
+        <v>119817200</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,39 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552569</v>
+        <v>552555</v>
       </c>
       <c r="R4" t="n">
-        <v>7064094</v>
+        <v>7064110</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819370</v>
+        <v>119818914</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1050,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552629</v>
+        <v>552569</v>
       </c>
       <c r="R5" t="n">
-        <v>7064013</v>
+        <v>7064094</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119817200</v>
+        <v>119819370</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,34 +1133,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552555</v>
+        <v>552629</v>
       </c>
       <c r="R6" t="n">
-        <v>7064110</v>
+        <v>7064013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 37171-2024 artfynd.xlsx
+++ b/artfynd/A 37171-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819214</v>
+        <v>119818914</v>
       </c>
       <c r="B2" t="n">
-        <v>78262</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552621</v>
+        <v>552569</v>
       </c>
       <c r="R2" t="n">
-        <v>7063985</v>
+        <v>7064094</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +753,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +780,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820977</v>
+        <v>119816855</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -810,14 +825,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552458</v>
+        <v>552478</v>
       </c>
       <c r="R3" t="n">
-        <v>7064130</v>
+        <v>7064146</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,9 +870,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119817200</v>
+        <v>119820205</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552555</v>
+        <v>552627</v>
       </c>
       <c r="R4" t="n">
-        <v>7064110</v>
+        <v>7063998</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119818914</v>
+        <v>119817200</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552569</v>
+        <v>552555</v>
       </c>
       <c r="R5" t="n">
-        <v>7064094</v>
+        <v>7064110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819370</v>
+        <v>119816881</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>4772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,46 +1150,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552629</v>
+        <v>552470</v>
       </c>
       <c r="R6" t="n">
-        <v>7064013</v>
+        <v>7064151</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,19 +1211,14 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:28</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119818013</v>
+        <v>119817132</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,37 +1261,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552609</v>
+        <v>552557</v>
       </c>
       <c r="R7" t="n">
-        <v>7064097</v>
+        <v>7064110</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819099</v>
+        <v>119820977</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1369,25 +1385,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552600</v>
+        <v>552458</v>
       </c>
       <c r="R8" t="n">
-        <v>7064081</v>
+        <v>7064130</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,19 +1434,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,22 +1451,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119816953</v>
+        <v>119819352</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,30 +1475,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1497,13 +1512,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552478</v>
+        <v>552618</v>
       </c>
       <c r="R9" t="n">
-        <v>7064143</v>
+        <v>7063975</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,19 +1545,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,19 +1562,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819352</v>
+        <v>119817130</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1602,29 +1607,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552618</v>
+        <v>552524</v>
       </c>
       <c r="R10" t="n">
-        <v>7063975</v>
+        <v>7064101</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,9 +1652,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,19 +1679,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119817015</v>
+        <v>119819370</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1721,14 +1732,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552494</v>
+        <v>552629</v>
       </c>
       <c r="R11" t="n">
-        <v>7064121</v>
+        <v>7064013</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1770,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119816855</v>
+        <v>119819214</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>78262</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,42 +1824,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552478</v>
+        <v>552621</v>
       </c>
       <c r="R12" t="n">
-        <v>7064146</v>
+        <v>7063985</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1875,19 +1881,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,22 +1898,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119816973</v>
+        <v>119817767</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,34 +1926,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552473</v>
+        <v>552552</v>
       </c>
       <c r="R13" t="n">
-        <v>7064101</v>
+        <v>7064113</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,9 +1988,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,22 +2015,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119817063</v>
+        <v>119816973</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2032,39 +2043,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552512</v>
+        <v>552473</v>
       </c>
       <c r="R14" t="n">
-        <v>7064119</v>
+        <v>7064101</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,19 +2100,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,22 +2117,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119816881</v>
+        <v>119818013</v>
       </c>
       <c r="B15" t="n">
-        <v>4772</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,25 +2141,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552470</v>
+        <v>552609</v>
       </c>
       <c r="R15" t="n">
-        <v>7064151</v>
+        <v>7064097</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2209,11 +2205,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819431</v>
+        <v>119817063</v>
       </c>
       <c r="B16" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2256,34 +2247,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552620</v>
+        <v>552512</v>
       </c>
       <c r="R16" t="n">
-        <v>7064000</v>
+        <v>7064119</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,7 +2311,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2325,7 +2321,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,10 +2348,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119817767</v>
+        <v>119819431</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2368,39 +2364,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552552</v>
+        <v>552620</v>
       </c>
       <c r="R17" t="n">
-        <v>7064113</v>
+        <v>7064000</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,7 +2423,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2442,7 +2433,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,7 +2460,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119817130</v>
+        <v>119817015</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2510,14 +2501,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552524</v>
+        <v>552494</v>
       </c>
       <c r="R18" t="n">
-        <v>7064101</v>
+        <v>7064121</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2540,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2550,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,7 +2577,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119820205</v>
+        <v>119819099</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2631,10 +2622,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552627</v>
+        <v>552600</v>
       </c>
       <c r="R19" t="n">
-        <v>7063998</v>
+        <v>7064081</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2666,7 +2657,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2676,7 +2667,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2703,10 +2694,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119817132</v>
+        <v>119816953</v>
       </c>
       <c r="B20" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2715,31 +2706,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2748,13 +2738,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552557</v>
+        <v>552478</v>
       </c>
       <c r="R20" t="n">
-        <v>7064110</v>
+        <v>7064143</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2781,9 +2771,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,12 +2798,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 37171-2024 artfynd.xlsx
+++ b/artfynd/A 37171-2024 artfynd.xlsx
@@ -2129,10 +2129,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119818013</v>
+        <v>119817063</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,37 +2145,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552609</v>
+        <v>552512</v>
       </c>
       <c r="R15" t="n">
-        <v>7064097</v>
+        <v>7064119</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2202,9 +2207,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,22 +2234,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119817063</v>
+        <v>119818013</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,42 +2262,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552512</v>
+        <v>552609</v>
       </c>
       <c r="R16" t="n">
-        <v>7064119</v>
+        <v>7064097</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2309,19 +2319,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,12 +2336,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 37171-2024 artfynd.xlsx
+++ b/artfynd/A 37171-2024 artfynd.xlsx
@@ -2129,10 +2129,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119817063</v>
+        <v>119818013</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,42 +2145,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552512</v>
+        <v>552609</v>
       </c>
       <c r="R15" t="n">
-        <v>7064119</v>
+        <v>7064097</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2207,19 +2202,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2234,22 +2219,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119818013</v>
+        <v>119817063</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2262,37 +2247,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552609</v>
+        <v>552512</v>
       </c>
       <c r="R16" t="n">
-        <v>7064097</v>
+        <v>7064119</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2319,9 +2309,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,12 +2336,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 37171-2024 artfynd.xlsx
+++ b/artfynd/A 37171-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119818914</v>
+        <v>119819352</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,25 +708,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552569</v>
+        <v>552618</v>
       </c>
       <c r="R2" t="n">
-        <v>7064094</v>
+        <v>7063975</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,19 +757,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:11</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119816855</v>
+        <v>119817063</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552478</v>
+        <v>552512</v>
       </c>
       <c r="R3" t="n">
-        <v>7064146</v>
+        <v>7064119</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820205</v>
+        <v>119817132</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,42 +919,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552627</v>
+        <v>552557</v>
       </c>
       <c r="R4" t="n">
-        <v>7063998</v>
+        <v>7064110</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,19 +981,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +998,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119817200</v>
+        <v>119816855</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1026,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552555</v>
+        <v>552478</v>
       </c>
       <c r="R5" t="n">
-        <v>7064110</v>
+        <v>7064146</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119816881</v>
+        <v>119817200</v>
       </c>
       <c r="B6" t="n">
-        <v>4772</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,41 +1139,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552470</v>
+        <v>552555</v>
       </c>
       <c r="R6" t="n">
-        <v>7064151</v>
+        <v>7064110</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,14 +1200,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119817132</v>
+        <v>119819214</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
+        <v>78278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,42 +1255,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552557</v>
+        <v>552621</v>
       </c>
       <c r="R7" t="n">
-        <v>7064110</v>
+        <v>7063985</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119820977</v>
+        <v>119818914</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,29 +1374,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552458</v>
+        <v>552569</v>
       </c>
       <c r="R8" t="n">
-        <v>7064130</v>
+        <v>7064094</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,9 +1419,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,22 +1446,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819352</v>
+        <v>119816973</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,46 +1474,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552618</v>
+        <v>552473</v>
       </c>
       <c r="R9" t="n">
-        <v>7063975</v>
+        <v>7064101</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119817130</v>
+        <v>119819431</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,39 +1576,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552524</v>
+        <v>552620</v>
       </c>
       <c r="R10" t="n">
-        <v>7064101</v>
+        <v>7064000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,7 +1635,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,7 +1645,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819370</v>
+        <v>119816881</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>4772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,46 +1684,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552629</v>
+        <v>552470</v>
       </c>
       <c r="R11" t="n">
-        <v>7064013</v>
+        <v>7064151</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1769,19 +1745,14 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:28</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,22 +1767,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819214</v>
+        <v>119818013</v>
       </c>
       <c r="B12" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,21 +1795,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1848,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552621</v>
+        <v>552609</v>
       </c>
       <c r="R12" t="n">
-        <v>7063985</v>
+        <v>7064097</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1910,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119817767</v>
+        <v>119820205</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,14 +1922,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552552</v>
+        <v>552627</v>
       </c>
       <c r="R13" t="n">
-        <v>7064113</v>
+        <v>7063998</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,7 +1961,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2000,7 +1971,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,10 +1998,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119816973</v>
+        <v>119819370</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,34 +2014,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552473</v>
+        <v>552629</v>
       </c>
       <c r="R14" t="n">
-        <v>7064101</v>
+        <v>7064013</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2100,9 +2076,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,22 +2103,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119818013</v>
+        <v>119817767</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,37 +2131,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552609</v>
+        <v>552552</v>
       </c>
       <c r="R15" t="n">
-        <v>7064097</v>
+        <v>7064113</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2202,9 +2193,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,22 +2220,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119817063</v>
+        <v>119817015</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2276,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552512</v>
+        <v>552494</v>
       </c>
       <c r="R16" t="n">
-        <v>7064119</v>
+        <v>7064121</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2321,7 +2322,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,10 +2349,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819431</v>
+        <v>119819099</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2364,34 +2365,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552620</v>
+        <v>552600</v>
       </c>
       <c r="R17" t="n">
-        <v>7064000</v>
+        <v>7064081</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2423,7 +2429,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2433,7 +2439,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,10 +2466,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119817015</v>
+        <v>119817130</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,14 +2507,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552494</v>
+        <v>552524</v>
       </c>
       <c r="R18" t="n">
-        <v>7064121</v>
+        <v>7064101</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2550,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819099</v>
+        <v>119820977</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,25 +2616,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552600</v>
+        <v>552458</v>
       </c>
       <c r="R19" t="n">
-        <v>7064081</v>
+        <v>7064130</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2655,19 +2665,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2682,12 +2682,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2697,7 +2697,7 @@
         <v>119816953</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 37171-2024 artfynd.xlsx
+++ b/artfynd/A 37171-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819352</v>
+        <v>119817767</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -708,14 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552618</v>
+        <v>552552</v>
       </c>
       <c r="R2" t="n">
-        <v>7063975</v>
+        <v>7064113</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,9 +753,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119817063</v>
+        <v>119817132</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,27 +808,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552512</v>
+        <v>552557</v>
       </c>
       <c r="R3" t="n">
-        <v>7064119</v>
+        <v>7064110</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,19 +870,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119817132</v>
+        <v>119819352</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,27 +915,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552557</v>
+        <v>552618</v>
       </c>
       <c r="R4" t="n">
-        <v>7064110</v>
+        <v>7063975</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119816855</v>
+        <v>119817063</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552478</v>
+        <v>552512</v>
       </c>
       <c r="R5" t="n">
-        <v>7064146</v>
+        <v>7064119</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119817200</v>
+        <v>119816881</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>4772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,41 +1139,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552555</v>
+        <v>552470</v>
       </c>
       <c r="R6" t="n">
-        <v>7064110</v>
+        <v>7064151</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,19 +1200,14 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:03</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1222,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819214</v>
+        <v>119819370</v>
       </c>
       <c r="B7" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,37 +1250,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552621</v>
+        <v>552629</v>
       </c>
       <c r="R7" t="n">
-        <v>7063985</v>
+        <v>7064013</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,9 +1312,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,19 +1339,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119818914</v>
+        <v>119817130</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1386,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552569</v>
+        <v>552524</v>
       </c>
       <c r="R8" t="n">
-        <v>7064094</v>
+        <v>7064101</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119816973</v>
+        <v>119820977</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,37 +1484,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552473</v>
+        <v>552458</v>
       </c>
       <c r="R9" t="n">
-        <v>7064101</v>
+        <v>7064130</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819431</v>
+        <v>119817015</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,34 +1595,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552620</v>
+        <v>552494</v>
       </c>
       <c r="R10" t="n">
-        <v>7064000</v>
+        <v>7064121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1645,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119816881</v>
+        <v>119820205</v>
       </c>
       <c r="B11" t="n">
-        <v>4772</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,41 +1708,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552470</v>
+        <v>552627</v>
       </c>
       <c r="R11" t="n">
-        <v>7064151</v>
+        <v>7063998</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1745,14 +1774,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,22 +1801,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119818013</v>
+        <v>119819099</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,37 +1829,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552609</v>
+        <v>552600</v>
       </c>
       <c r="R12" t="n">
-        <v>7064097</v>
+        <v>7064081</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,9 +1891,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,19 +1918,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119820205</v>
+        <v>119818914</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1926,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552627</v>
+        <v>552569</v>
       </c>
       <c r="R13" t="n">
-        <v>7063998</v>
+        <v>7064094</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1971,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,7 +2047,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819370</v>
+        <v>119816855</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2039,14 +2088,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552629</v>
+        <v>552478</v>
       </c>
       <c r="R14" t="n">
-        <v>7064013</v>
+        <v>7064146</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2088,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119817767</v>
+        <v>119819214</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,42 +2180,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552552</v>
+        <v>552621</v>
       </c>
       <c r="R15" t="n">
-        <v>7064113</v>
+        <v>7063985</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,19 +2237,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2220,22 +2254,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119817015</v>
+        <v>119816973</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2248,39 +2282,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552494</v>
+        <v>552473</v>
       </c>
       <c r="R16" t="n">
-        <v>7064121</v>
+        <v>7064101</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2310,19 +2339,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:51</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,22 +2356,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819099</v>
+        <v>119819431</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,39 +2384,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552600</v>
+        <v>552620</v>
       </c>
       <c r="R17" t="n">
-        <v>7064081</v>
+        <v>7064000</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2439,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119817130</v>
+        <v>119816953</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2478,43 +2492,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552524</v>
+        <v>552478</v>
       </c>
       <c r="R18" t="n">
-        <v>7064101</v>
+        <v>7064143</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,7 +2559,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2569,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2596,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119820977</v>
+        <v>119817200</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,46 +2612,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552458</v>
+        <v>552555</v>
       </c>
       <c r="R19" t="n">
-        <v>7064130</v>
+        <v>7064110</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2665,9 +2669,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2682,22 +2696,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119816953</v>
+        <v>119818013</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2706,45 +2720,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552478</v>
+        <v>552609</v>
       </c>
       <c r="R20" t="n">
-        <v>7064143</v>
+        <v>7064097</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2771,19 +2781,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,12 +2798,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 37171-2024 artfynd.xlsx
+++ b/artfynd/A 37171-2024 artfynd.xlsx
@@ -1930,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119818914</v>
+        <v>119819214</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,42 +1946,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552569</v>
+        <v>552621</v>
       </c>
       <c r="R13" t="n">
-        <v>7064094</v>
+        <v>7063985</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2008,19 +2003,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:11</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,19 +2020,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119816855</v>
+        <v>119818914</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2088,14 +2073,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552478</v>
+        <v>552569</v>
       </c>
       <c r="R14" t="n">
-        <v>7064146</v>
+        <v>7064094</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,7 +2112,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2122,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,10 +2149,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819214</v>
+        <v>119816855</v>
       </c>
       <c r="B15" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,37 +2165,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552621</v>
+        <v>552478</v>
       </c>
       <c r="R15" t="n">
-        <v>7063985</v>
+        <v>7064146</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2237,9 +2227,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2254,12 +2254,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 37171-2024 artfynd.xlsx
+++ b/artfynd/A 37171-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119817767</v>
+        <v>119817130</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -716,14 +716,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552552</v>
+        <v>552524</v>
       </c>
       <c r="R2" t="n">
-        <v>7064113</v>
+        <v>7064101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119817132</v>
+        <v>119816953</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,31 +804,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552557</v>
+        <v>552478</v>
       </c>
       <c r="R3" t="n">
-        <v>7064110</v>
+        <v>7064143</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,9 +869,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819352</v>
+        <v>119816973</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,46 +924,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552618</v>
+        <v>552473</v>
       </c>
       <c r="R4" t="n">
-        <v>7063975</v>
+        <v>7064101</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119817063</v>
+        <v>119818914</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1051,14 +1051,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552512</v>
+        <v>552569</v>
       </c>
       <c r="R5" t="n">
-        <v>7064119</v>
+        <v>7064094</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119816881</v>
+        <v>119817200</v>
       </c>
       <c r="B6" t="n">
-        <v>4772</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,41 +1139,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552470</v>
+        <v>552555</v>
       </c>
       <c r="R6" t="n">
-        <v>7064151</v>
+        <v>7064110</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,14 +1200,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,22 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819370</v>
+        <v>119819214</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,42 +1255,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552629</v>
+        <v>552621</v>
       </c>
       <c r="R7" t="n">
-        <v>7064013</v>
+        <v>7063985</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,19 +1312,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,19 +1329,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119817130</v>
+        <v>119819370</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1396,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552524</v>
+        <v>552629</v>
       </c>
       <c r="R8" t="n">
-        <v>7064101</v>
+        <v>7064013</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,7 +1458,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119820977</v>
+        <v>119817063</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1501,14 +1491,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1517,13 +1503,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552458</v>
+        <v>552512</v>
       </c>
       <c r="R9" t="n">
-        <v>7064130</v>
+        <v>7064119</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,9 +1536,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,19 +1563,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119817015</v>
+        <v>119819352</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1612,10 +1608,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552494</v>
+        <v>552618</v>
       </c>
       <c r="R10" t="n">
-        <v>7064121</v>
+        <v>7063975</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1657,19 +1657,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:51</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,22 +1674,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119820205</v>
+        <v>119817132</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,42 +1702,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552627</v>
+        <v>552557</v>
       </c>
       <c r="R11" t="n">
-        <v>7063998</v>
+        <v>7064110</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,19 +1764,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:33</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,22 +1781,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819099</v>
+        <v>119819431</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,39 +1809,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552600</v>
+        <v>552620</v>
       </c>
       <c r="R12" t="n">
-        <v>7064081</v>
+        <v>7064000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1893,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,7 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,10 +1905,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819214</v>
+        <v>119818013</v>
       </c>
       <c r="B13" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,21 +1921,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1970,10 +1945,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552621</v>
+        <v>552609</v>
       </c>
       <c r="R13" t="n">
-        <v>7063985</v>
+        <v>7064097</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2032,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119818914</v>
+        <v>119816881</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>4772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,46 +2019,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552569</v>
+        <v>552470</v>
       </c>
       <c r="R14" t="n">
-        <v>7064094</v>
+        <v>7064151</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2110,19 +2080,14 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:11</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:11</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,19 +2102,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119816855</v>
+        <v>119820977</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2182,10 +2147,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2194,13 +2163,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552478</v>
+        <v>552458</v>
       </c>
       <c r="R15" t="n">
-        <v>7064146</v>
+        <v>7064130</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2227,19 +2196,9 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2254,22 +2213,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119816973</v>
+        <v>119817015</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2282,34 +2241,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552473</v>
+        <v>552494</v>
       </c>
       <c r="R16" t="n">
-        <v>7064101</v>
+        <v>7064121</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,9 +2303,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,22 +2330,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819431</v>
+        <v>119816855</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,34 +2358,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stortjärnen, Stortjärnen, Ång</t>
+          <t>Tegelhusudden, Tegelhusudden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552620</v>
+        <v>552478</v>
       </c>
       <c r="R17" t="n">
-        <v>7064000</v>
+        <v>7064146</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,7 +2422,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2432,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2459,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119816953</v>
+        <v>119817767</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,30 +2471,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2524,10 +2504,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552478</v>
+        <v>552552</v>
       </c>
       <c r="R18" t="n">
-        <v>7064143</v>
+        <v>7064113</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2559,7 +2539,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,7 +2549,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2596,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119817200</v>
+        <v>119819099</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2612,34 +2592,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552555</v>
+        <v>552600</v>
       </c>
       <c r="R19" t="n">
-        <v>7064110</v>
+        <v>7064081</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,7 +2656,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2666,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119818013</v>
+        <v>119820205</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,37 +2709,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tegelhusudden, Tegelhusudden, Ång</t>
+          <t>Stortjärnen, Stortjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552609</v>
+        <v>552627</v>
       </c>
       <c r="R20" t="n">
-        <v>7064097</v>
+        <v>7063998</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2781,9 +2771,19 @@
           <t>2024-09-17</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,12 +2798,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
